--- a/Actividadesv1/PRD_Proctor_Demo.xlsx
+++ b/Actividadesv1/PRD_Proctor_Demo.xlsx
@@ -790,7 +790,7 @@
         <v>19</v>
       </c>
       <c r="D20" t="str">
-        <v>Máxima densidad seca MDS (g/cm³)</v>
+        <v>Máxima densidad seca (g/cm³)</v>
       </c>
       <c r="E20" t="str">
         <v>numerico-fx[PUNTOMAXIMOY(#17A:#17D, #18A:#18D, 3)]:dec[3]</v>
@@ -810,7 +810,7 @@
         <v>20</v>
       </c>
       <c r="D21" t="str">
-        <v>Óptimo contenido de humedad OCH (%)</v>
+        <v>Humedad óptima (%)</v>
       </c>
       <c r="E21" t="str">
         <v>numerico-fx[PUNTOMAXIMOX(#17A:#17D, #18A:#18D, 3)]:dec[2]</v>
